--- a/sample.xlsx
+++ b/sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Moleesh\IdeaProjects\weighbridge-v1.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63BB93AC-C7D2-4429-BEC4-90940B701FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251FF848-F030-4BF4-9860-64EAD758B363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Sl.No</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Operator Gross</t>
+  </si>
+  <si>
+    <t>Weighing Data</t>
   </si>
 </sst>
 </file>
@@ -463,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AB4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.36328125" bestFit="1" customWidth="1"/>
@@ -490,9 +493,10 @@
     <col min="25" max="25" width="7.6328125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11.90625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="8" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,8 +578,11 @@
       <c r="AA1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>-1</v>
       </c>
@@ -613,7 +620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>-2</v>
       </c>
@@ -651,7 +658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>-3</v>
       </c>
